--- a/data/housing-starts.xlsx
+++ b/data/housing-starts.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" customWidth="1" style="2" min="1" max="1"/>
@@ -431,11 +431,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>238.05</v>
+        <v>250.9</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -445,11 +445,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254.06</v>
+        <v>238.05</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -459,11 +459,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>232.76</v>
+        <v>254.06</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -473,11 +473,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>279.23</v>
+        <v>232.76</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -487,11 +487,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>245.79</v>
+        <v>279.23</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -501,11 +501,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>294.08</v>
+        <v>245.79</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -515,11 +515,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>283.73</v>
+        <v>294.08</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -529,11 +529,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>279.51</v>
+        <v>283.73</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -543,11 +543,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>278.61</v>
+        <v>279.51</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -557,11 +557,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>229.03</v>
+        <v>278.61</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -571,11 +571,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>239.74</v>
+        <v>229.03</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -585,11 +585,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>231.47</v>
+        <v>239.74</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -599,11 +599,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>262.44</v>
+        <v>231.47</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -611,26 +611,25 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>231.468</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>262.44</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
         <v/>
       </c>
-      <c r="D15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2024-11-01</t>
-        </is>
+      <c r="A16" s="6" t="n">
+        <v>45627</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>262.44</v>
+        <v>231.468</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
@@ -639,11 +638,13 @@
       <c r="D16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>45566</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>242.21</v>
+        <v>262.44</v>
       </c>
       <c r="C17">
         <f>(B17/B29-1)*100</f>
@@ -653,10 +654,10 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>224.43</v>
+        <v>242.21</v>
       </c>
       <c r="C18">
         <f>(B18/B30-1)*100</f>
@@ -666,10 +667,10 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>213.54</v>
+        <v>224.43</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -679,10 +680,10 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>275.4</v>
+        <v>213.54</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -692,10 +693,10 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>241.59</v>
+        <v>45474</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>275.4</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -705,10 +706,10 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>266.83</v>
+        <v>241.59</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -718,10 +719,10 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>241.4</v>
+        <v>266.83</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -731,10 +732,10 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>243.09</v>
+        <v>241.4</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -744,10 +745,10 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>261.29</v>
+        <v>243.09</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -757,10 +758,10 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>231.86</v>
+        <v>261.29</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -770,10 +771,10 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>248.01</v>
+        <v>231.86</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -783,10 +784,10 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>210.68</v>
+        <v>248.01</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -796,10 +797,10 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>272.16</v>
+        <v>210.68</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -809,10 +810,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>266.28</v>
+        <v>272.16</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -822,10 +823,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>247.31</v>
+        <v>266.28</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -835,10 +836,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>253.17</v>
+        <v>247.31</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -848,10 +849,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>281.06</v>
+        <v>253.17</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -861,10 +862,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>196.33</v>
+        <v>281.06</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -874,10 +875,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>261.26</v>
+        <v>196.33</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -887,10 +888,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>213.4</v>
+        <v>261.26</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -900,10 +901,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>240.77</v>
+        <v>213.4</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -913,22 +914,23 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B38" s="1" t="n">
-        <v>209.47</v>
+        <v>44958</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>240.77</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
         <v/>
       </c>
+      <c r="D38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>250.78</v>
+        <v>209.47</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -937,10 +939,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>262.3</v>
+        <v>250.78</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -949,10 +951,10 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>262.96</v>
+        <v>262.3</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -961,10 +963,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>295.34</v>
+        <v>262.96</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -973,10 +975,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>266.38</v>
+        <v>295.34</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -985,10 +987,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>277.4</v>
+        <v>266.38</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -997,10 +999,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>273.51</v>
+        <v>277.4</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -1009,10 +1011,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>281.7</v>
+        <v>273.51</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -1021,10 +1023,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>263.1</v>
+        <v>281.7</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1033,10 +1035,10 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>243.16</v>
+        <v>263.1</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1045,10 +1047,10 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>244.36</v>
+        <v>243.16</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1057,10 +1059,10 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>229.48</v>
+        <v>244.36</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1069,10 +1071,10 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>247.18</v>
+        <v>229.48</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1081,10 +1083,10 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>306.2</v>
+        <v>247.18</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1093,10 +1095,10 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>236.96</v>
+        <v>306.2</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1105,10 +1107,10 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>253.65</v>
+        <v>236.96</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1117,10 +1119,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>260.85</v>
+        <v>253.65</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1129,10 +1131,10 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>274.12</v>
+        <v>260.85</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1141,10 +1143,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>281.29</v>
+        <v>274.12</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1153,10 +1155,10 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>281.3</v>
+        <v>281.29</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1165,10 +1167,10 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>268.94</v>
+        <v>281.3</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1177,10 +1179,10 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>321.28</v>
+        <v>268.94</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1189,10 +1191,10 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>267.98</v>
+        <v>321.28</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1201,10 +1203,10 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>295.59</v>
+        <v>267.98</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1213,10 +1215,10 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>240.42</v>
+        <v>295.59</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1225,10 +1227,10 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>259.93</v>
+        <v>240.42</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
@@ -1237,10 +1239,10 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>227.49</v>
+        <v>259.93</v>
       </c>
       <c r="C65">
         <f>(B65/B77-1)*100</f>
@@ -1248,7 +1250,12 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n"/>
+      <c r="A66" s="3" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>227.49</v>
+      </c>
       <c r="C66">
         <f>(B66/B78-1)*100</f>
         <v/>
@@ -1338,6 +1345,13 @@
         <v/>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="3" t="n"/>
+      <c r="C79">
+        <f>(B79/B91-1)*100</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/housing-starts.xlsx
+++ b/data/housing-starts.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" customWidth="1" style="2" min="1" max="1"/>
@@ -431,11 +431,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>250.9</v>
+        <v>235.85</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -445,11 +445,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>238.05</v>
+        <v>250.9</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -459,11 +459,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254.06</v>
+        <v>238.05</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -473,11 +473,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>232.76</v>
+        <v>254.06</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -487,11 +487,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>279.23</v>
+        <v>232.76</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -501,11 +501,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>245.79</v>
+        <v>279.23</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -515,11 +515,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>294.08</v>
+        <v>245.79</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -529,11 +529,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>283.73</v>
+        <v>294.08</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -543,11 +543,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>279.51</v>
+        <v>283.73</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -557,11 +557,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>278.61</v>
+        <v>279.51</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -571,11 +571,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>229.03</v>
+        <v>278.61</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -585,11 +585,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>239.74</v>
+        <v>229.03</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -599,11 +599,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>231.47</v>
+        <v>239.74</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -613,11 +613,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>262.44</v>
+        <v>231.47</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
@@ -625,26 +625,25 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>231.468</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>262.44</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
         <v/>
       </c>
-      <c r="D16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2024-11-01</t>
-        </is>
+      <c r="A17" s="6" t="n">
+        <v>45627</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>262.44</v>
+        <v>231.468</v>
       </c>
       <c r="C17">
         <f>(B17/B29-1)*100</f>
@@ -653,11 +652,13 @@
       <c r="D17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>45566</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>242.21</v>
+        <v>262.44</v>
       </c>
       <c r="C18">
         <f>(B18/B30-1)*100</f>
@@ -667,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>224.43</v>
+        <v>242.21</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -680,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>213.54</v>
+        <v>224.43</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -693,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>275.4</v>
+        <v>213.54</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -706,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>241.59</v>
+        <v>45474</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>275.4</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -719,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>266.83</v>
+        <v>241.59</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -732,10 +733,10 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>241.4</v>
+        <v>266.83</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -745,10 +746,10 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>243.09</v>
+        <v>241.4</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -758,10 +759,10 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>261.29</v>
+        <v>243.09</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -771,10 +772,10 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>231.86</v>
+        <v>261.29</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -784,10 +785,10 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>248.01</v>
+        <v>231.86</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -797,10 +798,10 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>210.68</v>
+        <v>248.01</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -810,10 +811,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>272.16</v>
+        <v>210.68</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -823,10 +824,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>266.28</v>
+        <v>272.16</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -836,10 +837,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>247.31</v>
+        <v>266.28</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -849,10 +850,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>253.17</v>
+        <v>247.31</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -862,10 +863,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>281.06</v>
+        <v>253.17</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -875,10 +876,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>196.33</v>
+        <v>281.06</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -888,10 +889,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>261.26</v>
+        <v>196.33</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -901,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>213.4</v>
+        <v>261.26</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -914,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>240.77</v>
+        <v>213.4</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -927,22 +928,23 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B39" s="1" t="n">
-        <v>209.47</v>
+        <v>44958</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>240.77</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
         <v/>
       </c>
+      <c r="D39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>250.78</v>
+        <v>209.47</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -951,10 +953,10 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>262.3</v>
+        <v>250.78</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -963,10 +965,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>262.96</v>
+        <v>262.3</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -975,10 +977,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>295.34</v>
+        <v>262.96</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -987,10 +989,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>266.38</v>
+        <v>295.34</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -999,10 +1001,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>277.4</v>
+        <v>266.38</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -1011,10 +1013,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>273.51</v>
+        <v>277.4</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -1023,10 +1025,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>281.7</v>
+        <v>273.51</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1035,10 +1037,10 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>263.1</v>
+        <v>281.7</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1047,10 +1049,10 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>243.16</v>
+        <v>263.1</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1059,10 +1061,10 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>244.36</v>
+        <v>243.16</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1071,10 +1073,10 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>229.48</v>
+        <v>244.36</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1083,10 +1085,10 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>247.18</v>
+        <v>229.48</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1095,10 +1097,10 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>306.2</v>
+        <v>247.18</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1107,10 +1109,10 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>236.96</v>
+        <v>306.2</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1119,10 +1121,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>253.65</v>
+        <v>236.96</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1131,10 +1133,10 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>260.85</v>
+        <v>253.65</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1143,10 +1145,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>274.12</v>
+        <v>260.85</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1155,10 +1157,10 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>281.29</v>
+        <v>274.12</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1167,10 +1169,10 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>281.3</v>
+        <v>281.29</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1179,10 +1181,10 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>268.94</v>
+        <v>281.3</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1191,10 +1193,10 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>321.28</v>
+        <v>268.94</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1203,10 +1205,10 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>267.98</v>
+        <v>321.28</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1215,10 +1217,10 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>295.59</v>
+        <v>267.98</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1227,10 +1229,10 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>240.42</v>
+        <v>295.59</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
@@ -1239,10 +1241,10 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>259.93</v>
+        <v>240.42</v>
       </c>
       <c r="C65">
         <f>(B65/B77-1)*100</f>
@@ -1251,10 +1253,10 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>227.49</v>
+        <v>259.93</v>
       </c>
       <c r="C66">
         <f>(B66/B78-1)*100</f>
@@ -1262,7 +1264,12 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n"/>
+      <c r="A67" s="3" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>227.49</v>
+      </c>
       <c r="C67">
         <f>(B67/B79-1)*100</f>
         <v/>
@@ -1352,6 +1359,13 @@
         <v/>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="3" t="n"/>
+      <c r="C80">
+        <f>(B80/B92-1)*100</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/housing-starts.xlsx
+++ b/data/housing-starts.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" customWidth="1" style="2" min="1" max="1"/>
@@ -431,11 +431,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>235.85</v>
+        <v>279.32</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -445,11 +445,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>250.9</v>
+        <v>235.85</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -459,11 +459,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>238.05</v>
+        <v>250.9</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -473,11 +473,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254.06</v>
+        <v>238.05</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -487,11 +487,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>232.76</v>
+        <v>254.06</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -501,11 +501,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>279.23</v>
+        <v>232.76</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -515,11 +515,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>245.79</v>
+        <v>279.23</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -529,11 +529,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>294.08</v>
+        <v>245.79</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -543,11 +543,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>283.73</v>
+        <v>294.08</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -557,11 +557,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>279.51</v>
+        <v>283.73</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -571,11 +571,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>278.61</v>
+        <v>279.51</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -585,11 +585,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>229.03</v>
+        <v>278.61</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -599,11 +599,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>239.74</v>
+        <v>229.03</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -613,11 +613,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>231.47</v>
+        <v>239.74</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
@@ -627,11 +627,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>262.44</v>
+        <v>231.47</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
@@ -639,26 +639,25 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>231.468</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>262.44</v>
       </c>
       <c r="C17">
         <f>(B17/B29-1)*100</f>
         <v/>
       </c>
-      <c r="D17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2024-11-01</t>
-        </is>
+      <c r="A18" s="6" t="n">
+        <v>45627</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>262.44</v>
+        <v>231.468</v>
       </c>
       <c r="C18">
         <f>(B18/B30-1)*100</f>
@@ -667,11 +666,13 @@
       <c r="D18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>45566</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>242.21</v>
+        <v>262.44</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -681,10 +682,10 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>224.43</v>
+        <v>242.21</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -694,10 +695,10 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>213.54</v>
+        <v>224.43</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -707,10 +708,10 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>275.4</v>
+        <v>213.54</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -720,10 +721,10 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>241.59</v>
+        <v>45474</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>275.4</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -733,10 +734,10 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>266.83</v>
+        <v>241.59</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -746,10 +747,10 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>241.4</v>
+        <v>266.83</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -759,10 +760,10 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>243.09</v>
+        <v>241.4</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -772,10 +773,10 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>261.29</v>
+        <v>243.09</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -785,10 +786,10 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>231.86</v>
+        <v>261.29</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -798,10 +799,10 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>248.01</v>
+        <v>231.86</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -811,10 +812,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>210.68</v>
+        <v>248.01</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -824,10 +825,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>272.16</v>
+        <v>210.68</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -837,10 +838,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>266.28</v>
+        <v>272.16</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -850,10 +851,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>247.31</v>
+        <v>266.28</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -863,10 +864,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>253.17</v>
+        <v>247.31</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -876,10 +877,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>281.06</v>
+        <v>253.17</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -889,10 +890,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>196.33</v>
+        <v>281.06</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -902,10 +903,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>261.26</v>
+        <v>196.33</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -915,10 +916,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>213.4</v>
+        <v>261.26</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -928,10 +929,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>240.77</v>
+        <v>213.4</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -941,22 +942,23 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B40" s="1" t="n">
-        <v>209.47</v>
+        <v>44958</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>240.77</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
         <v/>
       </c>
+      <c r="D40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>250.78</v>
+        <v>209.47</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -965,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>262.3</v>
+        <v>250.78</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -977,10 +979,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>262.96</v>
+        <v>262.3</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -989,10 +991,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>295.34</v>
+        <v>262.96</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -1001,10 +1003,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>266.38</v>
+        <v>295.34</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -1013,10 +1015,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>277.4</v>
+        <v>266.38</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -1025,10 +1027,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>273.51</v>
+        <v>277.4</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1037,10 +1039,10 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>281.7</v>
+        <v>273.51</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1049,10 +1051,10 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>263.1</v>
+        <v>281.7</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1061,10 +1063,10 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>243.16</v>
+        <v>263.1</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1073,10 +1075,10 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>244.36</v>
+        <v>243.16</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1085,10 +1087,10 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>229.48</v>
+        <v>244.36</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1097,10 +1099,10 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>247.18</v>
+        <v>229.48</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1109,10 +1111,10 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>306.2</v>
+        <v>247.18</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1121,10 +1123,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>236.96</v>
+        <v>306.2</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1133,10 +1135,10 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>253.65</v>
+        <v>236.96</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1145,10 +1147,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>260.85</v>
+        <v>253.65</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1157,10 +1159,10 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>274.12</v>
+        <v>260.85</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1169,10 +1171,10 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>281.29</v>
+        <v>274.12</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1181,10 +1183,10 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>281.3</v>
+        <v>281.29</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1193,10 +1195,10 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>268.94</v>
+        <v>281.3</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1205,10 +1207,10 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>321.28</v>
+        <v>268.94</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1217,10 +1219,10 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>267.98</v>
+        <v>321.28</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1229,10 +1231,10 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>295.59</v>
+        <v>267.98</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
@@ -1241,10 +1243,10 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>240.42</v>
+        <v>295.59</v>
       </c>
       <c r="C65">
         <f>(B65/B77-1)*100</f>
@@ -1253,10 +1255,10 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>259.93</v>
+        <v>240.42</v>
       </c>
       <c r="C66">
         <f>(B66/B78-1)*100</f>
@@ -1265,10 +1267,10 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>227.49</v>
+        <v>259.93</v>
       </c>
       <c r="C67">
         <f>(B67/B79-1)*100</f>
@@ -1276,7 +1278,12 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n"/>
+      <c r="A68" s="3" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>227.49</v>
+      </c>
       <c r="C68">
         <f>(B68/B80-1)*100</f>
         <v/>
@@ -1366,6 +1373,13 @@
         <v/>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="3" t="n"/>
+      <c r="C81">
+        <f>(B81/B93-1)*100</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/housing-starts.xlsx
+++ b/data/housing-starts.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" customWidth="1" style="2" min="1" max="1"/>
@@ -431,11 +431,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>279.32</v>
+        <v>261.38</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -445,11 +445,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>235.85</v>
+        <v>279.32</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -459,11 +459,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>250.9</v>
+        <v>235.85</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -473,11 +473,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>238.05</v>
+        <v>250.9</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -487,11 +487,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254.06</v>
+        <v>238.05</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -501,11 +501,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>232.76</v>
+        <v>254.06</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -515,11 +515,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>279.23</v>
+        <v>232.76</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -529,11 +529,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>245.79</v>
+        <v>279.23</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -543,11 +543,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>294.08</v>
+        <v>245.79</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -557,11 +557,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>283.73</v>
+        <v>294.08</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -571,11 +571,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>279.51</v>
+        <v>283.73</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -585,11 +585,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>278.61</v>
+        <v>279.51</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -599,11 +599,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>229.03</v>
+        <v>278.61</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -613,11 +613,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>239.74</v>
+        <v>229.03</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
@@ -627,11 +627,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>231.47</v>
+        <v>239.74</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
@@ -641,11 +641,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>262.44</v>
+        <v>231.47</v>
       </c>
       <c r="C17">
         <f>(B17/B29-1)*100</f>
@@ -653,26 +653,25 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>231.468</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>262.44</v>
       </c>
       <c r="C18">
         <f>(B18/B30-1)*100</f>
         <v/>
       </c>
-      <c r="D18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2024-11-01</t>
-        </is>
+      <c r="A19" s="6" t="n">
+        <v>45627</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>262.44</v>
+        <v>231.468</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -681,11 +680,13 @@
       <c r="D19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>45566</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>242.21</v>
+        <v>262.44</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -695,10 +696,10 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>224.43</v>
+        <v>242.21</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -708,10 +709,10 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>213.54</v>
+        <v>224.43</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -721,10 +722,10 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>275.4</v>
+        <v>213.54</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -734,10 +735,10 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>241.59</v>
+        <v>45474</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>275.4</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -747,10 +748,10 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>266.83</v>
+        <v>241.59</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -760,10 +761,10 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>241.4</v>
+        <v>266.83</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -773,10 +774,10 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>243.09</v>
+        <v>241.4</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -786,10 +787,10 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>261.29</v>
+        <v>243.09</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -799,10 +800,10 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>231.86</v>
+        <v>261.29</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -812,10 +813,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>248.01</v>
+        <v>231.86</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -825,10 +826,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>210.68</v>
+        <v>248.01</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -838,10 +839,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>272.16</v>
+        <v>210.68</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -851,10 +852,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>266.28</v>
+        <v>272.16</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -864,10 +865,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>247.31</v>
+        <v>266.28</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -877,10 +878,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>253.17</v>
+        <v>247.31</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -890,10 +891,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>281.06</v>
+        <v>253.17</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -903,10 +904,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>196.33</v>
+        <v>281.06</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -916,10 +917,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>261.26</v>
+        <v>196.33</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -929,10 +930,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>213.4</v>
+        <v>261.26</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -942,10 +943,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>240.77</v>
+        <v>213.4</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -955,22 +956,23 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B41" s="1" t="n">
-        <v>209.47</v>
+        <v>44958</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>240.77</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
         <v/>
       </c>
+      <c r="D41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>250.78</v>
+        <v>209.47</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -979,10 +981,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>262.3</v>
+        <v>250.78</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -991,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>262.96</v>
+        <v>262.3</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -1003,10 +1005,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>295.34</v>
+        <v>262.96</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -1015,10 +1017,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>266.38</v>
+        <v>295.34</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -1027,10 +1029,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>277.4</v>
+        <v>266.38</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1039,10 +1041,10 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>273.51</v>
+        <v>277.4</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1051,10 +1053,10 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>281.7</v>
+        <v>273.51</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1063,10 +1065,10 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>263.1</v>
+        <v>281.7</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1075,10 +1077,10 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>243.16</v>
+        <v>263.1</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1087,10 +1089,10 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>244.36</v>
+        <v>243.16</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1099,10 +1101,10 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>229.48</v>
+        <v>244.36</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1111,10 +1113,10 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>247.18</v>
+        <v>229.48</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1123,10 +1125,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>306.2</v>
+        <v>247.18</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1135,10 +1137,10 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>236.96</v>
+        <v>306.2</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1147,10 +1149,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>253.65</v>
+        <v>236.96</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1159,10 +1161,10 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>260.85</v>
+        <v>253.65</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1171,10 +1173,10 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>274.12</v>
+        <v>260.85</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1183,10 +1185,10 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>281.29</v>
+        <v>274.12</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1195,10 +1197,10 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>281.3</v>
+        <v>281.29</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1207,10 +1209,10 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>268.94</v>
+        <v>281.3</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1219,10 +1221,10 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>321.28</v>
+        <v>268.94</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1231,10 +1233,10 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>267.98</v>
+        <v>321.28</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
@@ -1243,10 +1245,10 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>295.59</v>
+        <v>267.98</v>
       </c>
       <c r="C65">
         <f>(B65/B77-1)*100</f>
@@ -1255,10 +1257,10 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>240.42</v>
+        <v>295.59</v>
       </c>
       <c r="C66">
         <f>(B66/B78-1)*100</f>
@@ -1267,10 +1269,10 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>259.93</v>
+        <v>240.42</v>
       </c>
       <c r="C67">
         <f>(B67/B79-1)*100</f>
@@ -1279,10 +1281,10 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>227.49</v>
+        <v>259.93</v>
       </c>
       <c r="C68">
         <f>(B68/B80-1)*100</f>
@@ -1290,7 +1292,12 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n"/>
+      <c r="A69" s="3" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>227.49</v>
+      </c>
       <c r="C69">
         <f>(B69/B81-1)*100</f>
         <v/>
@@ -1380,6 +1387,13 @@
         <v/>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="3" t="n"/>
+      <c r="C82">
+        <f>(B82/B94-1)*100</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
